--- a/output/pdf_financials_xlsx/SHRP.xlsx
+++ b/output/pdf_financials_xlsx/SHRP.xlsx
@@ -3362,25 +3362,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06324299999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.06324299999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.074271</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.0988</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.0988</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.06887</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.098605</v>
       </c>
     </row>
     <row r="93">
@@ -5452,7 +5452,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -5920,7 +5924,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -6538,7 +6546,11 @@
           <t>Share-based payment reserve 6</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -6708,7 +6720,11 @@
           <t>Share-based payment reserve 4,5</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SHRP.xlsx
+++ b/output/pdf_financials_xlsx/SHRP.xlsx
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.079181</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.389625</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.332619</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.180892</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.458471</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.008168999999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.059904</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.062175</v>
       </c>
     </row>
     <row r="35">
@@ -1553,28 +1553,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.079181</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.389625</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.332619</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.180892</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.458471</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.008168999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.059904</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.062175</v>
       </c>
     </row>
     <row r="37">
@@ -1931,22 +1931,22 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.337661</v>
+        <v>0.005042</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.184359</v>
+        <v>0.003467</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.462623</v>
+        <v>0.004152</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.016055</v>
+        <v>0.007886000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.067914</v>
+        <v>0.00801</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.069912</v>
+        <v>0.007737</v>
       </c>
     </row>
     <row r="49">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/SHRP.xlsx
+++ b/output/pdf_financials_xlsx/SHRP.xlsx
@@ -4251,16 +4251,16 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.09227200000000001</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.389802</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>0.116719</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -7364,7 +7364,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -8028,7 +8032,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>0.09227200000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/SHRP.xlsx
+++ b/output/pdf_financials_xlsx/SHRP.xlsx
@@ -3563,10 +3563,8 @@
       <c r="E99" s="3" t="n">
         <v>-0.208139</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-0.147568</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-0.043058</v>
@@ -3596,10 +3594,8 @@
       <c r="E100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -3629,10 +3625,8 @@
       <c r="E101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -3662,10 +3656,8 @@
       <c r="E102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>0</v>
@@ -3695,13 +3687,11 @@
       <c r="E103" s="3" t="n">
         <v>-0.007086</v>
       </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="3" t="n">
+        <v>-0.012349</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.016036</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>0</v>
@@ -3728,10 +3718,8 @@
       <c r="E104" s="3" t="n">
         <v>-0.00353</v>
       </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" s="3" t="n">
+        <v>0.001162</v>
       </c>
       <c r="G104" s="3" t="n">
         <v>0.023083</v>
@@ -3761,10 +3749,8 @@
       <c r="E105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
@@ -3794,13 +3780,11 @@
       <c r="E106" s="3" t="n">
         <v>-0.010616</v>
       </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" s="3" t="n">
+        <v>-0.011187</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.023083</v>
+        <v>0.039119</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>-0.021336</v>
@@ -3827,10 +3811,8 @@
       <c r="E107" s="3" t="n">
         <v>0.026332</v>
       </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" s="3" t="n">
+        <v>0.0382</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0</v>
@@ -3860,10 +3842,8 @@
       <c r="E108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
@@ -3893,10 +3873,8 @@
       <c r="E109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G109" s="3" t="n">
         <v>0</v>
@@ -3926,10 +3904,8 @@
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -3959,10 +3935,8 @@
       <c r="E111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -3992,10 +3966,8 @@
       <c r="E112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -4025,10 +3997,8 @@
       <c r="E113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G113" s="3" t="n">
         <v>0</v>
@@ -4058,10 +4028,8 @@
       <c r="E114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -4091,10 +4059,8 @@
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -4124,10 +4090,8 @@
       <c r="E116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -4157,10 +4121,8 @@
       <c r="E117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G117" s="3" t="n">
         <v>0</v>
@@ -4190,10 +4152,8 @@
       <c r="E118" s="3" t="n">
         <v>-0.181942</v>
       </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F118" s="3" t="n">
+        <v>-0.050537</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>-0.428729</v>
@@ -4229,10 +4189,8 @@
       <c r="E119" s="3" t="n">
         <v>-0.231942</v>
       </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F119" s="3" t="n">
+        <v>-0.050537</v>
       </c>
       <c r="G119" s="3" t="n">
         <v>-0.377478</v>
@@ -4262,10 +4220,8 @@
       <c r="E120" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F120" s="3" t="n">
+        <v>0.462424</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
@@ -4295,10 +4251,8 @@
       <c r="E121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -4328,10 +4282,8 @@
       <c r="E122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G122" s="3" t="n">
         <v>0</v>
@@ -4361,10 +4313,8 @@
       <c r="E123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
@@ -4394,10 +4344,8 @@
       <c r="E124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -4427,10 +4375,8 @@
       <c r="E125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -4460,10 +4406,8 @@
       <c r="E126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>0</v>
@@ -4540,10 +4484,8 @@
       <c r="E128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
@@ -4579,10 +4521,8 @@
       <c r="E129" s="3" t="n">
         <v>0.299999</v>
       </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F129" s="3" t="n">
+        <v>0.462424</v>
       </c>
       <c r="G129" s="3" t="n">
         <v>0</v>
@@ -4659,10 +4599,8 @@
       <c r="E131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G131" s="3" t="n">
         <v>0</v>
@@ -4692,10 +4630,8 @@
       <c r="E132" s="3" t="n">
         <v>-0.151727</v>
       </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F132" s="3" t="n">
+        <v>0.277579</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>-0.450302</v>
@@ -4772,10 +4708,8 @@
       <c r="E134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -4805,10 +4739,8 @@
       <c r="E135" s="3" t="n">
         <v>-0.219784</v>
       </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F135" s="3" t="n">
+        <v>-0.134308</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.072824</v>
@@ -4831,7 +4763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6797,10 +6729,8 @@
       <c r="H36" s="5" t="n">
         <v>-0.208139</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="5" t="n">
+        <v>-0.147568</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>-0.043058</v>
@@ -6955,10 +6885,8 @@
       <c r="H39" s="5" t="n">
         <v>-0.00353</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="5" t="n">
+        <v>0.001162</v>
       </c>
       <c r="J39" s="5" t="n">
         <v>0.023083</v>
@@ -7003,10 +6931,8 @@
       <c r="H40" s="5" t="n">
         <v>-0.219784</v>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="5" t="n">
+        <v>-0.134308</v>
       </c>
       <c r="J40" s="5" t="n">
         <v>-0.072824</v>
@@ -7057,10 +6983,8 @@
       <c r="H41" s="5" t="n">
         <v>-0.181942</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="5" t="n">
+        <v>-0.050537</v>
       </c>
       <c r="J41" s="5" t="n">
         <v>-0.428729</v>
@@ -7658,15 +7582,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H52" s="5" t="n">
+        <v>-0.027362</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>-0.013753</v>
       </c>
       <c r="J52" s="5" t="n">
         <v>-0.068885</v>
@@ -7721,10 +7641,8 @@
       <c r="H53" s="5" t="n">
         <v>-0.231942</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="5" t="n">
+        <v>-0.050537</v>
       </c>
       <c r="J53" s="5" t="n">
         <v>-0.377478</v>
@@ -7744,10 +7662,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Item not effecting cash</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>June 30, 2021 June</t>
+          <t>Reversal of flow-through share premium liability</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -7761,21 +7683,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>0.00202</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.027362</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>-0.013753</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>-0.068885</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7801,19 +7721,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Reversal of flow-through share premium liability</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Stock based compensation</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F55" s="5" t="n">
+        <v>0.047939</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7821,12 +7743,10 @@
         </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>-0.027362</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.026332</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.0382</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -7852,17 +7772,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>Receivables and prepaid expenses</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7870,26 +7790,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>0.047939</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.001575</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.026332</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.007086</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>-0.012349</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0.016036</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -7910,39 +7826,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital item</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Receivables and prepaid expenses</t>
+          <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.001575</v>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.09227200000000001</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.389802</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>-0.007086</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.462424</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -7968,24 +7880,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Purchase of Bakar claims</t>
+          <t>Cash provided by financing activity</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="5" t="n">
+        <v>0.09227200000000001</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.389802</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7993,12 +7901,10 @@
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.462424</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -8029,19 +7935,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Issuance of shares, net of issuance costs</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>IssuanceOfCapitalStock</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0.09227200000000001</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>0.389802</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -8049,17 +7959,13 @@
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.151727</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.277579</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-0.450302</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8085,33 +7991,29 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash provided by financing activity</t>
+          <t>Cash, beginning</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>0.09227200000000001</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.389802</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.079181</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.389625</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.332619</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0.180892</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0.458471</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8137,39 +8039,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Decrease in cash</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, ending $</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>0.079181</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.389625</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.057006</v>
+        <v>0.332619</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>-0.151727</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.180892</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>0.458471</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>0.008168999999999999</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -8190,28 +8080,38 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financing activity</t>
+          <t>Supplemental non-cash transactions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cash, beginning</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Interest paid $</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>0.079181</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.389625</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>0.332619</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -8242,26 +8142,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financing activity</t>
+          <t>Supplemental non-cash transactions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cash, ending $</t>
+          <t>Taxes paid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>0.079181</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.389625</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.332619</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>0.180892</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -8292,15 +8200,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Supplemental non-cash transactions</t>
+          <t>Items not effecting cash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation asset $</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Stock based compensation</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -8317,12 +8229,10 @@
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.026332</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.0382</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -8348,30 +8258,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Year-ended          To</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>June 30, 2019 June</t>
+          <t>Purchase of Bakar claims</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>3e-05</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H65" s="5" t="n">
+        <v>-0.05</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -8402,34 +8314,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital item</t>
+          <t>Supplemental non-cash transactions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>-0.0205</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.017033</v>
+          <t>Shares issued for exploration and evaluation asset $</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H66" s="5" t="n">
+        <v>0.08</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -8458,36 +8368,28 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Financing activity</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>0.079181</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0.310444</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>June 30, 2021 June</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -8513,16 +8415,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Financing activity</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Note June 30, 2025 June</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Decrease in cash</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -8533,15 +8443,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G68" s="5" t="n">
+        <v>-0.057006</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>-0.151727</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -8553,43 +8459,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K68" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>3e-05</v>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Year-ended          To</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>General and administrative 6 $</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>June 30, 2019 June</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8611,95 +8513,101 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K69" s="5" t="n">
-        <v>0.051328</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>0.052281</v>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>-0.0205</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0.017033</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H70" s="5" t="n">
-        <v>0.031379</v>
-      </c>
-      <c r="I70" s="5" t="n">
-        <v>0.025043</v>
-      </c>
-      <c r="J70" s="5" t="n">
-        <v>0.013969</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>0.018542</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>0.017539</v>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Consulting fees 8</t>
+          <t>Increase in cash</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.079181</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.310444</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8721,11 +8629,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K71" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>0.018</v>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -8734,21 +8646,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Note June 30, 2025 June</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -8764,20 +8668,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H72" s="5" t="n">
-        <v>0.144245</v>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>0.034146</v>
-      </c>
-      <c r="J72" s="5" t="n">
-        <v>0.02705</v>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K72" s="5" t="n">
-        <v>0.02667</v>
+        <v>0.002024</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>0.02566</v>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="73">
@@ -8793,10 +8703,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Stock-based compensation 7</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>General and administrative 6 $</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -8828,10 +8742,10 @@
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0.020938</v>
+        <v>0.051328</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.029735</v>
+        <v>0.052281</v>
       </c>
     </row>
     <row r="74">
@@ -8847,12 +8761,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8871,19 +8785,19 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>-0.208139</v>
+        <v>0.031379</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>-0.147568</v>
+        <v>0.025043</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-0.043058</v>
+        <v>0.013969</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.135478</v>
+        <v>0.018542</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.143215</v>
+        <v>0.017539</v>
       </c>
     </row>
     <row r="75">
@@ -8899,12 +8813,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Consulting fees 8</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8922,20 +8836,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H75" s="5" t="n">
-        <v>8.639904</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>13.589904</v>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>15.631</v>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K75" s="5" t="n">
-        <v>18.736026</v>
+        <v>0.018</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>20.683602</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="76">
@@ -8951,12 +8871,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8975,19 +8895,19 @@
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.144245</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.034146</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>0</v>
+        <v>0.02705</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.02667</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.02566</v>
       </c>
     </row>
     <row r="77">
@@ -9003,7 +8923,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity 711,897 125,000 (8,281) 74,000 - 20,938 (135,478) 788,076 49,375 29,735</t>
+          <t>Stock-based compensation 7</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -9038,10 +8958,10 @@
         </is>
       </c>
       <c r="K77" s="5" t="n">
-        <v>0.723971</v>
+        <v>0.020938</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.143215</v>
+        <v>0.029735</v>
       </c>
     </row>
     <row r="78">
@@ -9057,10 +8977,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Deficit (586,097) - - - 50,868 - (135,478) (670,707) - -</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -9076,23 +9000,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H78" s="5" t="n">
+        <v>-0.208139</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>-0.147568</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>-0.043058</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.813922</v>
+        <v>-0.135478</v>
       </c>
       <c r="L78" s="5" t="n">
         <v>-0.143215</v>
@@ -9111,10 +9029,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Share-based payment reserve       98,800 - - - (50,868) 20,938 -       68,870 - 29,735 -       98,605          $             $                                                                                                                                                                                                                                                statements.</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -9130,30 +9052,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H79" s="5" t="n">
+        <v>8.639904</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>13.589904</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>15.631</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>18.736026</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>20.683602</v>
       </c>
     </row>
     <row r="80">
@@ -9164,15 +9076,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Share                                                                                                                                                                                                                                                                                                                                                                                                         integral</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Share                                                                                                                                                                                                                                                                                                                                                                                                         integral an Number 15,631,000 3,125,000 1,480,000 20,236,000</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -9188,26 +9104,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>21.2235</v>
+        <v>-1e-08</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.9875</v>
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="81">
@@ -9216,10 +9126,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Note June 30, 2024 June</t>
+          <t>Total shareholders’ equity 711,897 125,000 (8,281) 74,000 - 20,938 (135,478) 788,076 49,375 29,735</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -9248,16 +9162,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J81" s="5" t="n">
-        <v>0.002023</v>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.723971</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>-0.143215</v>
       </c>
     </row>
     <row r="82">
@@ -9273,14 +9187,10 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>General and administrative $</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Deficit (586,097) - - - 50,868 - (135,478) (670,707) - -</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -9296,22 +9206,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H82" s="5" t="n">
-        <v>0.033545</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>0.054932</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>0.052924</v>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K82" s="5" t="n">
-        <v>0.051328</v>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.813922</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>-0.143215</v>
       </c>
     </row>
     <row r="83">
@@ -9327,14 +9241,10 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Consulting fees 9</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based payment reserve       98,800 - - - (50,868) 20,938 -       68,870 - 29,735 -       98,605          $             $                                                                                                                                                                                                                                                statements.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -9355,14 +9265,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="5" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>0.018</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -9378,12 +9294,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share                                                                                                                                                                                                                                                                                                                                                                                                         integral</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Stock-based compensation 8</t>
+          <t>Share                                                                                                                                                                                                                                                                                                                                                                                                         integral an Number 15,631,000 3,125,000 1,480,000 20,236,000</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -9402,11 +9318,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H84" s="5" t="n">
-        <v>0.026332</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>0.0382</v>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -9414,12 +9334,10 @@
         </is>
       </c>
       <c r="K84" s="5" t="n">
-        <v>0.020938</v>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.2235</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>0.9875</v>
       </c>
     </row>
     <row r="85">
@@ -9428,14 +9346,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Reversal of flow-through share premium liability 7</t>
+          <t>Note June 30, 2024 June</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -9454,19 +9368,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H85" s="5" t="n">
-        <v>-0.027362</v>
-      </c>
-      <c r="I85" s="5" t="n">
-        <v>-0.013753</v>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>-0.068885</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -9487,10 +9403,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity 754,955 (43,058) 711,897 125,000 (8,281) 74,000 - 20,938</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>General and administrative $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -9506,21 +9426,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H86" s="5" t="n">
+        <v>0.033545</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>0.054932</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>0.788076</v>
+        <v>0.052924</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.135478</v>
+        <v>0.051328</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -9541,10 +9457,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Deficit (543,039) (43,058) (586,097) - - - 50,868 -</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Consulting fees 9</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -9565,16 +9485,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="5" t="n">
+        <v>0.008999999999999999</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>-0.6707070000000001</v>
+        <v>0.018</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.135478</v>
+        <v>0.018</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -9595,7 +9513,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>reserve       98,800 -       98,800 - - - (50,868)                                                                 Share-based payment                                                              20,938 -       68,870                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             statements.          $          $</t>
+          <t>Stock-based compensation 8</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -9614,25 +9532,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H88" s="5" t="n">
+        <v>0.026332</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>0.0382</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K88" s="5" t="n">
+        <v>0.020938</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -9648,12 +9560,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>$          $                                  capital                                                                                                                                                                                                     part</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>$          $                                  capital                                                                                                                                                                                                     part</t>
+          <t>Reversal of flow-through share premium liability 7</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -9672,20 +9584,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H89" s="5" t="n">
+        <v>-0.027362</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>-0.013753</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.068885</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -9704,10 +9610,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Note June 30, 2023 June</t>
+          <t>Total shareholders’ equity 754,955 (43,058) 711,897 125,000 (8,281) 74,000 - 20,938</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -9731,16 +9641,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="5" t="n">
-        <v>0.002022</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.788076</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.135478</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -9756,12 +9666,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Note    Number       Amount         reserve           Deficit           equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2021 10,631,000 $ 806,770 $ 74,271 $</t>
+          <t>Deficit (543,039) (43,058) (586,097) - - - 50,868 -</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -9785,16 +9695,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n">
-        <v>0.471899</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.409142</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.6707070000000001</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>-0.135478</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -9810,12 +9720,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Note    Number       Amount         reserve           Deficit           equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Shares issued for cash 7,8 5,000,000 400,000 -</t>
+          <t>reserve       98,800 -       98,800 - - - (50,868)                                                                 Share-based payment                                                              20,938 -       68,870                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             statements.          $          $</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -9839,8 +9749,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n">
-        <v>0.4</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -9866,12 +9778,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Note    Number       Amount         reserve           Deficit           equity</t>
+          <t>$          $                                  capital                                                                                                                                                                                                     part</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Share issuance costs 8 - (7,576) -</t>
+          <t>$          $                                  capital                                                                                                                                                                                                     part</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -9895,8 +9807,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="5" t="n">
-        <v>-0.007576</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -9920,14 +9834,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Note    Number       Amount         reserve           Deficit           equity</t>
-        </is>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Expiry of options 8 - - (13,671)</t>
+          <t>Note June 30, 2023 June</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -9951,13 +9861,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" s="5" t="n">
+        <v>0.002022</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>0.013671</v>
+        <v>3e-05</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -9983,7 +9891,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Stock-based compensation 8 - - 38,200</t>
+          <t>Balance, June 30, 2021 10,631,000 $ 806,770 $ 74,271 $</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -10008,12 +9916,10 @@
         </is>
       </c>
       <c r="I95" s="5" t="n">
-        <v>0.0382</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.471899</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>-0.409142</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -10039,14 +9945,10 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss - - -</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued for cash 7,8 5,000,000 400,000 -</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -10068,10 +9970,12 @@
         </is>
       </c>
       <c r="I96" s="5" t="n">
-        <v>-0.147568</v>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>-0.147568</v>
+        <v>0.4</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -10097,7 +10001,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2022 15,631,000 1,199,194 98,800</t>
+          <t>Share issuance costs 8 - (7,576) -</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -10122,10 +10026,12 @@
         </is>
       </c>
       <c r="I97" s="5" t="n">
-        <v>0.754955</v>
-      </c>
-      <c r="J97" s="5" t="n">
-        <v>-0.543039</v>
+        <v>-0.007576</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -10151,7 +10057,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2023 15,631,000 $ 1,199,194 $ 98,800 $</t>
+          <t>Expiry of options 8 - - (13,671)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -10175,11 +10081,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="5" t="n">
-        <v>0.711897</v>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.586097</v>
+        <v>0.013671</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -10198,10 +10106,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Note    Number       Amount         reserve           Deficit           equity</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Note June 30, 2022 June</t>
+          <t>Stock-based compensation 8 - - 38,200</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -10220,11 +10132,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="5" t="n">
-        <v>0.002021</v>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.0382</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -10250,15 +10164,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>$             $                                  capital                                                                                                                                                                                                part</t>
+          <t>Note    Number       Amount         reserve           Deficit           equity</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>$             $                                  capital                                                                                                                                                                                                part</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Net and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -10279,15 +10197,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" s="5" t="n">
+        <v>-0.147568</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>-0.147568</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -10306,10 +10220,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Note    Number       Amount         reserve           Deficit           equity</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Note June 30, 2021 June</t>
+          <t>Balance, June 30, 2022 15,631,000 1,199,194 98,800</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -10323,21 +10241,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G101" s="5" t="n">
-        <v>0.00202</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0.754955</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>-0.543039</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -10358,40 +10276,40 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Note    Number       Amount         reserve           Deficit           equity</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>General and administrative $</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>0.005044</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>0.022875</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>0.024221</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>0.033545</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, June 30, 2023 15,631,000 $ 1,199,194 $ 98,800 $</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>0.711897</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>-0.586097</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -10410,37 +10328,33 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Administrative expenses</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="n">
-        <v>0.017603</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>0.033229</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>0.01334</v>
+          <t>Note June 30, 2022 June</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0.031379</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002021</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -10466,12 +10380,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>$             $                                  capital                                                                                                                                                                                                part</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stock based compensation 6</t>
+          <t>$             $                                  capital                                                                                                                                                                                                part</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -10490,8 +10404,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H104" s="5" t="n">
-        <v>0.026332</v>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -10520,32 +10436,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Administrative expenses</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="n">
-        <v>0.003825</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>0.010406</v>
+          <t>Note June 30, 2021 June</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.037825</v>
+        <v>0.00202</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>0.144245</v>
+        <v>3e-05</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -10581,27 +10493,25 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Reversal of flow-through share premium liability 5</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>General and administrative $</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.005044</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0.022875</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.024221</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>-0.027362</v>
+        <v>0.033545</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -10637,25 +10547,25 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>-0.026472</v>
+        <v>0.017603</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>-0.114449</v>
+        <v>0.033229</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>-0.07538599999999999</v>
+        <v>0.01334</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>-0.208139</v>
+        <v>0.031379</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -10691,14 +10601,10 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Stock based compensation 6</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -10709,11 +10615,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G108" s="5" t="n">
-        <v>3.381</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>8.639904</v>
+        <v>0.026332</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -10749,25 +10657,25 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>0.003825</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.010406</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.037825</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.144245</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -10798,12 +10706,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>$         $                                  capital                                                                                                                                                                                                part</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>$         $                                  capital                                                                                                                                                                                                part</t>
+          <t>Reversal of flow-through share premium liability 5</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -10822,10 +10730,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H110" s="5" t="n">
+        <v>-0.027362</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -10856,30 +10762,30 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Note 6</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>-0.026472</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>-0.114449</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>6e-06</v>
+        <v>-0.07538599999999999</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>4e-06</v>
+        <v>-0.208139</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -10910,30 +10816,34 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2018)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Note June 30, 2019 June</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F112" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>3.381</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>8.639904</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10969,27 +10879,25 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Stock based compensation 4,5</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.047939</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -11020,12 +10928,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>$         $                                  capital                                                                                                                                                                                                part</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Weighted average number of outstanding shares</t>
+          <t>$         $                                  capital                                                                                                                                                                                                part</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -11034,8 +10942,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F114" s="5" t="n">
-        <v>2.621433</v>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -11076,32 +10986,30 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>$          $                                                                                          shareholders’</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>- - - (26,472)         (26,472) - - (114,449)          (140,921)                                                       Deficit</t>
+          <t>Note 6</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" s="5" t="n">
-        <v>0.06324299999999999</v>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G115" s="5" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>4e-06</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -11132,51 +11040,273 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>2018)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Note June 30, 2019 June</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Stock based compensation 4,5</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.047939</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Weighted average number of outstanding shares</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>2.621433</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>$          $                                                                                          shareholders’</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>- - - (26,472)         (26,472) - - (114,449)          (140,921)                                                       Deficit</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>0.06324299999999999</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
           <t>payment reserve                                                                                                                                                                                                                                                                                                                                                                      statements                                                                 Share-based</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>payment reserve                                                                                                                                                                                                                                                                                                                                                                      statements                                                                 Share-based          $          $</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t>-</t>
         </is>
